--- a/ig/revue-métier-exemples/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/ig/revue-métier-exemples/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-26T14:09:52+00:00</t>
+    <t>2023-04-26T14:28:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/revue-métier-exemples/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/ig/revue-métier-exemples/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-26T14:28:14+00:00</t>
+    <t>2023-04-26T14:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
